--- a/docs/reviews/SCS4_Review_Rows_20260924-7aed7be1.xlsx
+++ b/docs/reviews/SCS4_Review_Rows_20260924-7aed7be1.xlsx
@@ -11725,6 +11725,11 @@
       <c r="U141" t="n">
         <v>34</v>
       </c>
+      <c r="V141" t="inlineStr">
+        <is>
+          <t>SL-COOLING-SHEET-TWIN-GRAPHITE</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
@@ -13851,6 +13856,11 @@
       </c>
       <c r="U167" t="n">
         <v>110</v>
+      </c>
+      <c r="V167" t="inlineStr">
+        <is>
+          <t>SL-COOLING-SHEET-CAL-KING-WHITE</t>
+        </is>
       </c>
     </row>
     <row r="168">
@@ -43690,7 +43700,11 @@
       <c r="J5" t="n">
         <v>1</v>
       </c>
-      <c r="K5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>SL-COOLING-SHEET-TWIN-GRAPHITE</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -43902,7 +43916,11 @@
       <c r="J10" t="n">
         <v>1</v>
       </c>
-      <c r="K10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>SL-COOLING-SHEET-CAL-KING-WHITE</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
